--- a/artfynd/A 8846-2022 artfynd.xlsx
+++ b/artfynd/A 8846-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8846-2022 artfynd.xlsx
+++ b/artfynd/A 8846-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92705086</v>
+        <v>92705039</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>356476.9396596985</v>
+        <v>356549</v>
       </c>
       <c r="R2" t="n">
-        <v>6618235.971424524</v>
+        <v>6618151</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,19 +759,9 @@
           <t>2021-04-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-04-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92705143</v>
+        <v>92705058</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -860,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>356393.0048916821</v>
+        <v>356492</v>
       </c>
       <c r="R3" t="n">
-        <v>6618371.147270109</v>
+        <v>6618210</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,19 +873,9 @@
           <t>2021-04-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-04-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,6 +900,348 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>92705086</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gamla järnvägen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>356477</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6618236</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älgå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-04-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-04-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ingela Källén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ingela Källén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>92705111</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gamla järnvägen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>356451</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6618268</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älgå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-04-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-04-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ingela Källén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ingela Källén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>92705143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gamla järnvägen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>356393</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6618371</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älgå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-04-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-04-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ingela Källén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ingela Källén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
